--- a/Hardware/Electrical/Parts List.xlsx
+++ b/Hardware/Electrical/Parts List.xlsx
@@ -1,25 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzi\Desktop\Privat\github\lamp-2\Hardware\Electrical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA7AEC5-CA95-45AF-AEE3-931816D472B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="5000" yWindow="3430" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Supplier Part Nr</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Manufacturer Part Nr</t>
+  </si>
+  <si>
+    <t>Li-ion Cell 18650 3300mAh</t>
+  </si>
+  <si>
+    <t>Conrad</t>
+  </si>
+  <si>
+    <t>1558872 - 62</t>
+  </si>
+  <si>
+    <t>Panasonic</t>
+  </si>
+  <si>
+    <t>NCR18650GA</t>
+  </si>
+  <si>
+    <t>Total price</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -49,11 +113,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +395,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="19.90625" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1">
+        <f>G2*F2</f>
+        <v>19.8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Hardware/Electrical/Parts List.xlsx
+++ b/Hardware/Electrical/Parts List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzi\Desktop\Privat\github\lamp-2\Hardware\Electrical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA7AEC5-CA95-45AF-AEE3-931816D472B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DD0CD6-D827-41D0-BEC3-16A754BE3B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="3430" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
